--- a/Result/checksun_type/造紙.xlsx
+++ b/Result/checksun_type/造紙.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>37.755</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>37.83</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>38.11</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>37.83</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>38.11</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>37.77</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>38.13</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>38.13</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>37.775</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>37.87</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>38.15</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>37.87</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,7 +4641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>37.775</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>37.88</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>38.18</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>37.88</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>38.18</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,7 +5627,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>37.795</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>38.21</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>37.9</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>38.21</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,7 +6613,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>37.815</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>38.23</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>37.93</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>38.23</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,7 +7599,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>37.835</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>38.25</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>38.25</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,7 +8585,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>37.845</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>38.26</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>37.95</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,7 +9571,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>37.87</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>38.26</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>37.97</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>38.26</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10521,22 +10557,22 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>10.16</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>10.46</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11503,22 +11543,22 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>10.165</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>10.46</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12470,7 +12514,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -12485,22 +12529,22 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>10.155</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>10.46</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>10.48</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13452,7 +13500,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -13467,22 +13515,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>10.15</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>10.46</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>10.52</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14449,22 +14501,22 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>10.19</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>10.46</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15431,22 +15487,22 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>10.245</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>10.46</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>10.46</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16398,7 +16458,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -16413,22 +16473,22 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>10.305</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>10.47</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>10.365</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>10.47</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>10.435</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>10.47</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>10.73</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>10.47</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19344,7 +19416,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -19359,7 +19431,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -19369,12 +19441,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>28.55</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>29.38</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20326,7 +20402,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -20341,7 +20417,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -20351,12 +20427,12 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>28.645</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>29.38</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>29.01</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21308,7 +21388,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -21323,7 +21403,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -21333,12 +21413,12 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>28.73</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>29.39</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>29.39</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22290,7 +22374,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -22305,7 +22389,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -22315,12 +22399,12 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>28.79</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>29.37</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>29.18</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23272,7 +23360,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -23287,7 +23375,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -23297,12 +23385,12 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>28.905</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>29.28</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>29.38</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>29.28</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24254,7 +24346,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24269,22 +24361,22 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>28.995</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>29.38</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>29.39</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>29.38</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25236,7 +25332,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25251,22 +25347,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>29.07</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>29.49</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>29.4</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>29.49</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26218,7 +26318,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,22 +26333,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>29.085</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>29.37</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>29.56</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27200,7 +27304,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,22 +27319,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>29.105</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>29.33</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>29.33</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,7 +28290,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28197,7 +28305,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28207,12 +28315,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>10.8</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>11.12</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>10.92</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>11.12</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,7 +29276,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,7 +29291,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29189,12 +29301,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>10.815</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>11.13</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>10.94</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>11.13</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,7 +30262,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,7 +30277,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -30171,12 +30287,12 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>10.81</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>11.14</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,7 +31263,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -31153,12 +31273,12 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>10.81</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>11.14</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>10.99</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,7 +32249,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -32135,12 +32259,12 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>10.83</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>11.14</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>11.14</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33220,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,7 +33235,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -33117,12 +33245,12 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>10.87</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>11.06</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>11.15</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>11.06</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34206,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,22 +34221,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>10.91</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>11.16</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>11.16</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35056,7 +35192,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,22 +35207,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>10.935</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>11.16</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>11.16</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36038,7 +36178,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36053,22 +36193,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>10.97</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>11.17</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>11.18</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>11.17</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37020,7 +37164,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -37035,22 +37179,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37389,15 @@
           <t>13.085</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>13.31</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>13.18</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -38002,7 +38150,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38017,22 +38165,22 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38375,15 @@
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>13.34</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>13.23</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38984,7 +39136,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,22 +39151,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39361,15 @@
           <t>13.135</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>13.28</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>13.37</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>13.28</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39966,7 +40122,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39981,22 +40137,22 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40347,15 @@
           <t>13.145</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>13.38</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>13.31</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40948,7 +41108,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40963,22 +41123,22 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41333,15 @@
           <t>13.18</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>13.42</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>13.35</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41930,7 +42094,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -41945,22 +42109,22 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42319,15 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>13.45</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>13.37</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42912,7 +43080,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -42927,22 +43095,22 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43305,15 @@
           <t>13.235</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>13.48</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>13.48</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43894,7 +44066,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -43909,22 +44081,22 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44119,11 +44291,15 @@
           <t>13.24</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>13.52</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>13.52</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44876,7 +45052,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -44891,22 +45067,22 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45101,11 +45277,15 @@
           <t>13.24</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>13.56</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>13.56</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -45858,7 +46038,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -45873,7 +46053,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
@@ -45883,12 +46063,12 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46083,11 +46263,15 @@
           <t>24.62</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>24.68</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>24.03</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>24.68</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>24.03</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -46840,7 +47024,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -46855,7 +47039,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
@@ -46865,12 +47049,12 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47065,11 +47249,15 @@
           <t>24.64</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>23.98</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>24.69</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>23.98</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47822,7 +48010,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -47837,7 +48025,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
@@ -47847,12 +48035,12 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48047,11 +48235,15 @@
           <t>24.67</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>24.73</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>23.92</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>24.73</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>23.92</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48804,7 +48996,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -48819,7 +49011,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
@@ -48829,12 +49021,12 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49029,11 +49221,15 @@
           <t>24.69</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>23.86</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>24.76</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>23.86</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49786,7 +49982,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -49801,7 +49997,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
@@ -49811,12 +50007,12 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50011,11 +50207,15 @@
           <t>24.745</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>23.81</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>23.81</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50768,7 +50968,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -50783,7 +50983,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -50793,12 +50993,12 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -50993,11 +51193,15 @@
           <t>24.81</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>23.76</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>24.83</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>23.76</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51750,7 +51954,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -51765,22 +51969,22 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -51975,11 +52179,15 @@
           <t>24.78</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>23.71</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>24.86</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52732,7 +52940,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -52747,22 +52955,22 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -52957,11 +53165,15 @@
           <t>24.725</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>23.66</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>24.88</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>23.66</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53714,7 +53926,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53729,22 +53941,22 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -53939,11 +54151,15 @@
           <t>24.715</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>24.94</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>23.6</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>24.94</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54696,7 +54912,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -54711,7 +54927,7 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -54721,12 +54937,12 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -54921,11 +55137,15 @@
           <t>47.195</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>47.64</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>47.35</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>47.64</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55678,7 +55898,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -55693,7 +55913,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -55703,12 +55923,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -55903,11 +56123,15 @@
           <t>47.15499999999999</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>47.66</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>47.36</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>47.66</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56660,7 +56884,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -56675,7 +56899,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -56685,12 +56909,12 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -56885,11 +57109,15 @@
           <t>47.11</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>47.69</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>47.69</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57642,7 +57870,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -57657,7 +57885,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -57667,12 +57895,12 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -57867,11 +58095,15 @@
           <t>47.08</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>47.71</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>47.38</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>47.71</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58624,7 +58856,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -58639,7 +58871,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -58649,12 +58881,12 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -58849,11 +59081,15 @@
           <t>47.12</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>47.74</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>47.43</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>47.74</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59606,7 +59842,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -59621,7 +59857,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
@@ -59631,12 +59867,12 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -59831,11 +60067,15 @@
           <t>47.16</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>47.77</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>47.49</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>47.77</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60588,7 +60828,7 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60603,22 +60843,22 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -60813,11 +61053,15 @@
           <t>47.19500000000001</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>47.55</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>47.79</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>47.55</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>47.79</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61570,7 +61814,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61585,22 +61829,22 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -61795,11 +62039,15 @@
           <t>47.265</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>47.81</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>47.62</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>47.81</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62552,7 +62800,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62567,22 +62815,22 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -62777,11 +63025,15 @@
           <t>47.315</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>47.84</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>47.71</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>47.84</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
